--- a/artfynd/A 44407-2025 artfynd.xlsx
+++ b/artfynd/A 44407-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>65465216</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603021.631811836</v>
+        <v>603022</v>
       </c>
       <c r="R2" t="n">
-        <v>7022818.895682561</v>
+        <v>7022819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65465206</v>
+        <v>65465214</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603092.1676196019</v>
+        <v>603022</v>
       </c>
       <c r="R3" t="n">
-        <v>7022711.875431317</v>
+        <v>7022819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +845,11 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65465231</v>
+        <v>65465206</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,16 +890,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222395</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603199.4034210162</v>
+        <v>603092</v>
       </c>
       <c r="R4" t="n">
-        <v>7022920.394269777</v>
+        <v>7022712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,24 +947,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65465227</v>
+        <v>65465210</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222395</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603189.6054231588</v>
+        <v>603057</v>
       </c>
       <c r="R5" t="n">
-        <v>7022902.99034472</v>
+        <v>7022802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1044,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1076,7 @@
         <v>65465222</v>
       </c>
       <c r="B6" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603114.8135514859</v>
+        <v>603115</v>
       </c>
       <c r="R6" t="n">
-        <v>7022904.18506739</v>
+        <v>7022904</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1141,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65465214</v>
+        <v>65465231</v>
       </c>
       <c r="B7" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>222395</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603021.631811836</v>
+        <v>603199</v>
       </c>
       <c r="R7" t="n">
-        <v>7022818.895682561</v>
+        <v>7022920</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1238,14 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-07-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,11 +1256,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>gråal</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1359,230 +1269,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>65465210</v>
-      </c>
-      <c r="B8" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>222395</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dvärghäxört</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Circaea alpina</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Forsmo-Näsåker, Ång</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>603056.8629939066</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7022801.58769005</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>65465226</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Forsmo-Näsåker, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>603133.8085923246</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7022901.64721156</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
